--- a/www/download/COUNTRY.HUN.rpPE.xlsx
+++ b/www/download/COUNTRY.HUN.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Hungria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>124.999994757928</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>152.439020974766</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>186.219741832314</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>214.132754361592</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>236.966824914034</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>280.898870389336</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>286.532947285858</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>257.069406991601</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>224.215247886593</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>202.429153668107</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>199.203185952529</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>210.08403650247</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>183.486236851735</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170.356886305572</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200.723810528585</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.025</t>
+          <t>2.63230517730223</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.65976669149709</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.026</t>
+          <t>2.6025705375916</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.097</t>
+          <t>2.61232897970607</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.208</t>
+          <t>2.8774056946844</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.87860361910582</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.232</t>
+          <t>2.35170812408099</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.224</t>
+          <t>1.6766012561673</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>1.47718391115039</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.166</t>
+          <t>0.990027290626295</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.156</t>
+          <t>0.912308287893766</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.182</t>
+          <t>1.00901254997914</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.169</t>
+          <t>0.800919609457895</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.069</t>
+          <t>0.735571254567691</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.958</t>
+          <t>1.02568859029999</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.334</t>
+          <t>2.25033772949785</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.299</t>
+          <t>2.27292019139293</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.304</t>
+          <t>2.24233818242753</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.402</t>
+          <t>2.22278690644568</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.478</t>
+          <t>2.62216216603696</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.562</t>
+          <t>2.50270388672319</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.589</t>
+          <t>2.08892960633711</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.598</t>
+          <t>1.51408960890958</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.647</t>
+          <t>1.15370785227726</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.599</t>
+          <t>0.914041079348878</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.627</t>
+          <t>0.882477809428223</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.674</t>
+          <t>0.970325893404398</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.683</t>
+          <t>0.815820513327169</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.647</t>
+          <t>0.742509992672308</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.561</t>
+          <t>0.972509954415736</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8079.711</t>
+          <t>0.345950594408446</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8069.551</t>
+          <t>0.397422551057665</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8160.662</t>
+          <t>0.372502228091351</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8290.864</t>
+          <t>0.317499969101287</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8587.375</t>
+          <t>0.460456839081741</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8673.529</t>
+          <t>0.356657348188637</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8452.565</t>
+          <t>0.166497532176172</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8474.813</t>
+          <t>-0.0471168792189127</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8369.327</t>
+          <t>-0.443204405191894</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8304.772</t>
+          <t>-0.236362826585762</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8284.195</t>
+          <t>-0.240633056280129</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8317.391</t>
+          <t>-0.173261691288194</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>8277.404</t>
+          <t>-0.205948297048412</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>8076.164</t>
+          <t>-0.165105572275745</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7854.807</t>
+          <t>-0.0586290923130246</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6653.528</t>
+          <t>38455423032.4149</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6558.125</t>
+          <t>37006423069.7982</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6659.477</t>
+          <t>35569958007.4201</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6856.273</t>
+          <t>37931457597.9593</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7066.93</t>
+          <t>42297755539.6325</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6961.417</t>
+          <t>42381666902.7367</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7127.012</t>
+          <t>41291477973.7381</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7176.956</t>
+          <t>40886584565.1814</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7159.213</t>
+          <t>37758991610.0418</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7123.6</t>
+          <t>38666769270.4004</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7199.949</t>
+          <t>37446849334.3822</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7275.75</t>
+          <t>36801296193.2299</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7282.681</t>
+          <t>35060322376.2496</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7217.871</t>
+          <t>30240038589.344</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6982.465</t>
+          <t>28340957384.242</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>7277627710.3639</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>6986884303.18098</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>7215871109.92938</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>7834671466.55288</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>7639212426.59064</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>7940943819.15723</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>9329497664.52703</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>11553233930.7535</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>12802184039.1012</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>14984337229.5081</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>15277760664.9153</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>14341459083.3561</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>14791525577.8826</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>14765053997.3726</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33.11</t>
+          <t>12746333519.3651</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>14744351.3708348</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>13877829.3550209</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>13455679.7103868</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>14097280.7525852</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>61.57</t>
+          <t>15505531.9208614</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>15945139.0626878</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>61.15</t>
+          <t>13677737.5309127</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>61.57</t>
+          <t>11615904.9010892</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>58.22</t>
+          <t>8679388.81768541</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>7268479.77755881</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>6611879.35316846</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>6184630.40354293</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>59.38</t>
+          <t>4952746.87737877</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>3540302.80160183</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>4341045.12767176</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>67298.5810530403</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>66083.9877586799</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>64712.6310077447</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>65862.9089440313</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>71582.5208783358</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>70666.6102025676</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>66058.398619085</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>67319.9326813919</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>70812.2851952957</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>78126.7385436427</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>80675.2649834619</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>84561.897725362</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>92927.5997794594</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>96013.4198589481</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>90192.9305513718</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>126880.789547734</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>123515.797959821</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>116153.109987911</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>117514.741903709</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>132664.887160445</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>129324.697341914</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>121540.855796568</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>123562.70539722</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>132296.048320259</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>140734.89652173</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>147676.070106625</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>154322.996521878</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>173784.004410328</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>170311.539576578</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>147032.748271284</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>2.1235069461677</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>67.44</t>
+          <t>2.1531571231706</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>67.28</t>
+          <t>2.1169899058785</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>2.10647524146379</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>66.59</t>
+          <t>2.49923582424842</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>66.72</t>
+          <t>2.38411335547731</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>66.83</t>
+          <t>1.95942288580799</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>1.40248022930218</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>65.75</t>
+          <t>1.01247327898005</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>63.97</t>
+          <t>0.839904078611003</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>63.21</t>
+          <t>0.795629987302004</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>63.08</t>
+          <t>0.893024509071762</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>0.729642602382885</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>0.672951021695052</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>0.925355827256805</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>24304.5814167978</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>23651.167794313</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>21725.0215732598</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>20648.6634398311</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>20052.6737212134</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>17200.1115339258</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>17030.5062153724</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>19352.8263208026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>23410.4365570017</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>27383.1279901209</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>28516.1745862453</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>28261.7747013932</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>33488.6332777695</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>124.999994757928</t>
+          <t>2182.98531474748</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>152.439020974766</t>
+          <t>2118.01298874891</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>186.219741832314</t>
+          <t>2183.95325903322</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>214.132754361592</t>
+          <t>2303.10871468589</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>236.966824914034</t>
+          <t>2196.3865218217</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>280.898870389336</t>
+          <t>2229.13009390631</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>286.532947285858</t>
+          <t>2599.23168495477</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>257.069406991601</t>
+          <t>3210.99769616443</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>224.215247886593</t>
+          <t>3510.16637793194</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>202.429153668107</t>
+          <t>4163.05368271045</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>199.203185952529</t>
+          <t>4211.86255982459</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>210.08403650247</t>
+          <t>3904.03026523095</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>183.486236851735</t>
+          <t>4016.21350527216</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>170.356886305572</t>
+          <t>4049.02968913015</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>200.723810528585</t>
+          <t>3579.73794379827</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2585158356.01385</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2544898858.04886</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2635991551.1337</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2834283816.50266</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2914953968.52504</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2629583866.39958</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-1835923635.00269</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-1032620297.65453</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>-377040786.580085</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-855774196.840986</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>-317687063.6935</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>-122813584.734889</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>776012923.771893</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1346372395.90418</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>746959709.956831</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-2679307562.26353</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-2657105293.99125</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-2723217372.87605</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-2817065369.09144</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-2879032363.53407</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-2859819809.6393</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-2415359010.36533</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>-1860605770.58801</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>-786056304.462373</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>-1321231836.10539</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>-1147947863.81442</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>-1126420429.44165</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>-160819620.376403</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>489939205.042394</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-66539764.4583669</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>94149206.2496708</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>112206435.942394</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>87225821.7423505</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>-17218447.4112179</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>-35921604.9909672</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>230235943.239717</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>579435375.362634</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>827985472.933478</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>409015517.882288</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>465457639.264404</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>830260800.120916</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1003606844.70676</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>936832544.148296</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>856433190.861781</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>813499474.415198</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>6818.56979399584</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>6678.42774244146</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>6807.360263317</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>7154.55020057121</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>7685.67440105485</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>7543.62892188471</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>7692.2257339724</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>7714.3584813699</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>7064.11604036221</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>7659.61945029551</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>7562.94671481562</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>7390.42497624011</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>6946.61397898422</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>6773.82835530388</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>6892.2693101443</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>8153.35013983138</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>7916.74875146845</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>8034.35638529739</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>8472.37998929151</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>9073.63667598373</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>9235.15337309402</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>9029.58550035312</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>9001.94474458163</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>8273.52579864369</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>8984.44166607934</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>8845.56784066376</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>8653.3814318769</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>8111.75307681323</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>7811.45214312109</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>7965.74162454561</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>263.23</t>
+          <t>16317.3023958859</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>265.98</t>
+          <t>17439.8262165984</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>260.26</t>
+          <t>20632.6046639379</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>261.23</t>
+          <t>24583.8072247669</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>287.74</t>
+          <t>26340.2537911258</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>287.86</t>
+          <t>30283.0713820076</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>235.17</t>
+          <t>33065.2271460219</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>167.66</t>
+          <t>37475.6458533138</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>147.72</t>
+          <t>46029.4366018815</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>59362.4107947105</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>67510.2395437571</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>100.9</t>
+          <t>81417.6298164548</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>103086.968022661</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>73.56</t>
+          <t>116244.717550639</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>102.57</t>
+          <t>86121.6412323762</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>225.03</t>
+          <t>6972976738.98546</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>227.29</t>
+          <t>6796413280.69951</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>224.23</t>
+          <t>7056864052.48188</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>222.28</t>
+          <t>8362571511.23934</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>262.22</t>
+          <t>9439890027.20992</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>250.27</t>
+          <t>10523341269.4994</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>208.89</t>
+          <t>10635387044.491</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>151.41</t>
+          <t>10585567686.8461</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>115.37</t>
+          <t>10003970676.3826</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>11036697748.6132</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>11358111742.8157</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>97.03</t>
+          <t>12276837552.794</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>12855812460.2159</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>11350007003.717</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>9787376094.73248</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>18351.7452046612</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39.74</t>
+          <t>19801.5743993344</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>22427.2604938212</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>27128.315091272</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>29157.66171935</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>33386.6581357788</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>35449.8129193804</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>39852.588833931</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-44.32</t>
+          <t>50094.7183786812</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>63431.1063138496</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-24.06</t>
+          <t>70392.2969058567</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-17.33</t>
+          <t>83013.0779519612</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>101586.191481021</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>116238.965556102</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>81386.0289612402</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>32820.993</t>
+          <t>5172112030.55772</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31905.281</t>
+          <t>5130724384.43049</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>32348.874</t>
+          <t>5044940244.60238</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>34709.494</t>
+          <t>6511239928.09641</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>38185.62</t>
+          <t>7679583219.83114</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>39252.791</t>
+          <t>9237946321.85308</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>38209.937</t>
+          <t>9892701002.95915</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>38021.451</t>
+          <t>10625021867.9948</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>34970.034</t>
+          <t>11223581306.126</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>37429.238</t>
+          <t>11728499015.483</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>36761.003</t>
+          <t>12041336875.8351</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>36184.954</t>
+          <t>12652006635.2906</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>33818.239</t>
+          <t>13238365724.7857</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>31782.389</t>
+          <t>12695068755.5245</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>31527.98</t>
+          <t>9326257054.5487</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22731.721</t>
+          <t>-2034.44280877537</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22030.744</t>
+          <t>-2361.74818273608</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22491.797</t>
+          <t>-1794.65582988327</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>24338.213</t>
+          <t>-2544.50786650501</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>26731.406</t>
+          <t>-2817.40792822415</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>26873.054</t>
+          <t>-3103.58675377123</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>27609.929</t>
+          <t>-2384.5857733585</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>27756.416</t>
+          <t>-2376.94298061721</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>25764.053</t>
+          <t>-4065.28177679976</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27569.743</t>
+          <t>-4068.6955191391</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>27433.205</t>
+          <t>-2882.05736209961</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>27148.734</t>
+          <t>-1595.44813550641</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>25584.053</t>
+          <t>1500.77654164002</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>24701.212</t>
+          <t>5.75199453630395</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>24541.228</t>
+          <t>4735.61227113594</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>38455.423</t>
+          <t>1800864708.42774</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37006.423</t>
+          <t>1665688896.26902</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35569.958</t>
+          <t>2011923807.8795</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>37931.458</t>
+          <t>1851331583.14293</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>42297.756</t>
+          <t>1760306807.37878</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>42381.667</t>
+          <t>1285394947.64634</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>41291.478</t>
+          <t>742686041.53189</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>40886.585</t>
+          <t>-39454181.1486319</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>37758.992</t>
+          <t>-1219610629.74348</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>38666.769</t>
+          <t>-691801266.869773</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>37446.849</t>
+          <t>-683225133.019406</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>36801.296</t>
+          <t>-375169082.496629</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>35060.322</t>
+          <t>-382553264.569787</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>30240.039</t>
+          <t>-1345061751.80749</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>28340.957</t>
+          <t>461119040.183777</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>19987.24093</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>19839.50688</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>21004.95335</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>21506.88258</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>21052.34763</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>20218.01639</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>22287.38455</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>27489.32314</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>34425.34388</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>42627.21957</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>45109.00249</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>46021.06443</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>55049.77476</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>61036.95136</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>48116.3818</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20397.063</t>
+          <t>-0.0410738683150281</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19799.346</t>
+          <t>-0.0344291908447112</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19817.167</t>
+          <t>-0.0242670939838284</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>21259.257</t>
+          <t>-0.0172324492165466</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22822.768</t>
+          <t>-0.0124614418703762</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>23158.521</t>
+          <t>-0.010252537138698</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>22442.239</t>
+          <t>0.00741037300038007</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>22275.994</t>
+          <t>0.0159835358501152</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20210.736</t>
+          <t>0.0148345130957084</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>21465.242</t>
+          <t>0.0198230264854926</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>20457.17</t>
+          <t>0.0214324277259212</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>20165.416</t>
+          <t>0.0297520079050075</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>18747.822</t>
+          <t>0.0308227694530658</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>17047.873</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>17384.93</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>21148.7209385179</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>20803.7284565732</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>20896.892847196</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>21375.3848137194</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>21042.4432893277</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>20903.7686172109</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>23865.8383132277</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>30331.645055342</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>38730.082244585</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>46963.7342737843</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>51508.7043663024</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>52097.0567684416</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>63835.9978007698</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>71859.7339886758</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>58694.778280572</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7277.628</t>
+          <t>24971.7648136563</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6986.884</t>
+          <t>24752.0798094449</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7215.871</t>
+          <t>24891.6820905812</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>7834.671</t>
+          <t>25207.9121430708</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7639.212</t>
+          <t>24783.9985822109</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7940.944</t>
+          <t>25389.3433363619</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9329.498</t>
+          <t>27584.067228164</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>11553.234</t>
+          <t>34873.9763075699</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12802.184</t>
+          <t>44286.4464960014</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>14984.337</t>
+          <t>53622.4462388657</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15277.761</t>
+          <t>58247.945903252</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>14341.459</t>
+          <t>58545.1124246822</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>14791.526</t>
+          <t>71423.5215695397</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>14765.054</t>
+          <t>80623.5198120911</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>12746.334</t>
+          <t>65872.4146455416</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>212.35</t>
+          <t>254508.305141285</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>215.32</t>
+          <t>249505.11536862</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>211.7</t>
+          <t>236307.741572287</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>210.65</t>
+          <t>218297.248732917</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>249.92</t>
+          <t>215051.488527582</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>238.41</t>
+          <t>194374.693144571</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>195.94</t>
+          <t>201827.141007188</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>140.25</t>
+          <t>239499.926519695</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>101.25</t>
+          <t>286938.955093062</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>83.99</t>
+          <t>339376.053194343</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>79.56</t>
+          <t>361040.650152018</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>364782.048612521</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>430985.282906479</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>92.54</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>14.744</t>
+          <t>24971.7648136563</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.878</t>
+          <t>24775.7840494616</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13.456</t>
+          <t>25302.4336942737</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14.097</t>
+          <t>26190.3434797752</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15.506</t>
+          <t>27318.1584757885</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15.945</t>
+          <t>31058.6095478455</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.678</t>
+          <t>31658.271507544</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.616</t>
+          <t>32527.6414934527</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8.679</t>
+          <t>33952.2146604049</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7.268</t>
+          <t>35971.814201749</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6.612</t>
+          <t>37808.9184917026</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.185</t>
+          <t>38345.4618063611</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>4.953</t>
+          <t>39236.0631869847</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>40047.6064220182</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4.341</t>
+          <t>36328.8278319403</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21148.7209385179</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20822.9393252611</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>21187.0643231323</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>22186.2279949465</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>23072.8170770861</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>25635.8940397122</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>27194.2887541933</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>28131.6448231774</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>29536.4599401748</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>30943.8943744316</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>32789.0455548352</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>33583.7260163434</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>35055.1848610708</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>35097.9564721635</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>31443.9014030932</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>13850.9408063437</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>15060.9085605551</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>15990.5193994188</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>16886.8671869292</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>17372.8220977891</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>15207.2777736381</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>18526.120611836</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>23180.8819824301</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>27667.0362439986</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>34110.5884811343</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>36254.152226748</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>39114.7730953178</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>46772.7932904603</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>53384.4235179089</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>43149.8243844584</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>22731720704.9441</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>22030744009.3439</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>22491797411.7702</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>24338212935.8493</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>26731405792.1697</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>26873054033.5049</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>27609928901.4934</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>27756416103.1385</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>25764053291.276</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>27569743183.8546</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>27433205188.7449</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>27148733540.643</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>25584052793.7419</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>24701212170.2871</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>24541227517.6684</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>32820993007.2358</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>31905281226.5442</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>32348873732.5378</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>34709493837.2896</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>38185619618.1234</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>39252791136.9375</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>38209937127.5433</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>38021451004.0762</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>34970034160.6334</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>37429237887.5365</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>36761003485.2758</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>36184953835.3922</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>33818239270.8636</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>31782388679.9251</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>31527980000.1654</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20397062574.2543</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>19799345909.8454</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19817166907.8402</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>21259257327.356</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>22822768208.1445</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>23158521120.158</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>22442238814.9532</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>22275994294.9742</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>20210735819.5944</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>21465241725.9532</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>20457170147.2405</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>20165416140.1115</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>18747822142.6306</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>17047873143.8158</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>17384929760.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4025461</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4030099</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4026318</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4096782</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4208414</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4250367</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4231638</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4223693</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4226739</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4166006</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4155867</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4181597</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4169042</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4068691.46704218</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3957946.60261327</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3333796</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3298792</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3304041</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3401781</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3478082</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3562351</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3589329</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3598020</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3647173</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3599362</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3627317</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3673501</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3682953</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3646566</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3560689</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8079711219.40055</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8069551307.42483</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8160661798.29138</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8290864349.17157</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8587374640.12717</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8673528917</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8452564657</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8474813414</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8369326785</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>8304771954</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8284194674</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8317391408</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8277404373</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>8076163693.74774</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7854806818.35529</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6653528427.29386</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6558125225.49215</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6659476570.14462</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6856272880.13977</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>7066930465.10046</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6961416731.94834</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7127011526.85595</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7176955593.93508</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7159213271.18566</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7123600011.05471</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7199948537.14686</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7275750066.84333</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7282680540.18446</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7217871138.19669</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6982465348.42156</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.248673669020027</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.248673669020027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.248673669020027</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.248673669020027</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.274666085932445</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.264220981115569</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.260565849336195</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.260562595586571</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.232534470264458</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.29407658987496</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.301025358744711</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.306541028936287</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.307605667431767</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.32737349179284</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.331122973069948</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.613892332189813</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.613892332189813</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.613892332189813</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.613892332189813</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.615653264914631</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.606726649721676</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.611500965395145</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.615664483182112</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.582153996933471</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.596512468348034</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.592116281423768</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.594573862935085</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.593801367594568</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.579629299768395</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.585373655534772</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.13743399879016</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.13743399879016</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.13743399879016</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.13743399879016</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.109680649152924</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.129052369162755</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.127933185268661</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.123772921231317</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.185311532802071</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.109410941777007</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.106858359831521</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0988851081286282</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0985929649736658</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0929972084387651</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.08350337139528</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.260413920588253</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.262933092542137</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.264866997080023</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.268896858663875</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.287573805664277</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.279410572954901</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.279652578062721</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.282085772447841</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.290936560998481</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.314212894560748</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.322127152604479</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.325747420464897</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.321225903235019</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.343158586003545</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.348858261760017</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.677833029426623</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.674376320083935</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.672798001422632</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.671485645437709</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.665854820615166</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.667233439760036</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.668267932176083</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.668028192579496</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.657531004032354</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.639736854372774</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.632103324901836</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.630777419055233</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.633750410534317</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.610607396856165</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.610259375190225</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.061753049985124</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0626905873739285</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0623350014973444</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0596174958984162</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0465713737205574</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0533559872850632</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0520794897611961</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0498860349726628</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0515324349691658</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0460502510664775</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0457695224936847</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.04347516047987</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.045023686230664</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0462340171402905</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0408823630497574</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>91385.57973</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>94429.68677</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>97266.8189</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>101699.33222</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>104654.9122</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>104478.0818</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>115643.71912</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>138588.23325</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>172524.36307</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>208623.28951</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>228843.61944</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>242887.26422</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>293236.43547</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>335691.56586</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>264522.8033</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>38822.70562</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>39812.98837</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>40882.20149</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>42094.77933</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>42156.82068</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>40596.62111</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>46110.18784</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>58054.85829</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>71953.48274</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>87733.03472</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>94502.09813</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>97659.88552</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>118196.31486</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>134007.94333</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>109022.23903</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>31813537.022513</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>31357857.2603804</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>31103651.2424806</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>31134426.1538356</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>31302815.7833249</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>31668203.8084991</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>32157092.0553171</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>32756186.3130027</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>33389246.8345595</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>34196828.6281147</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>35181113.6314742</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>36082293.3732993</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>37043834.6988152</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
